--- a/Result/profitability/8028.xlsx
+++ b/Result/profitability/8028.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM48"/>
+  <dimension ref="A1:AM49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.87</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8775000000000001</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>31.87125</v>
+        <v>32.645</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -6526,6 +6526,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>8028</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>1427</v>
+      </c>
+      <c r="D49" t="n">
+        <v>886</v>
+      </c>
+      <c r="E49" t="n">
+        <v>541</v>
+      </c>
+      <c r="F49" t="n">
+        <v>37.89</v>
+      </c>
+      <c r="G49" t="n">
+        <v>370</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>25.94%</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>-11</v>
+      </c>
+      <c r="J49" t="n">
+        <v>359</v>
+      </c>
+      <c r="K49" t="n">
+        <v>308</v>
+      </c>
+      <c r="L49" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="M49" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N49" t="n">
+        <v>34.75375</v>
+      </c>
+      <c r="O49" t="n">
+        <v>1</v>
+      </c>
+      <c r="P49" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>1</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1</v>
+      </c>
+      <c r="S49" t="n">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
+      </c>
+      <c r="V49" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0.09999999999999987</v>
+      </c>
+      <c r="X49" t="n">
+        <v>0.06211180124223592</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0.3100000000000023</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>0.008249068653539249</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.948275862068966</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>5.880000000000003</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0.1836925960637301</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK49" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
